--- a/results/components/gene_names/p9s3.xlsx
+++ b/results/components/gene_names/p9s3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>gene1</t>
   </si>
@@ -22,28 +22,46 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>noc</t>
-  </si>
-  <si>
-    <t>tral</t>
-  </si>
-  <si>
-    <t>tud</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>sdt</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>Mmp1</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>Dat</t>
+  </si>
+  <si>
+    <t>cactin</t>
+  </si>
+  <si>
+    <t>PebIII</t>
+  </si>
+  <si>
+    <t>rad50</t>
+  </si>
+  <si>
+    <t>sec23</t>
+  </si>
+  <si>
+    <t>ird5</t>
+  </si>
+  <si>
+    <t>hyd</t>
   </si>
 </sst>
 </file>
@@ -375,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -418,6 +436,30 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/components/gene_names/p9s3.xlsx
+++ b/results/components/gene_names/p9s3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>gene1</t>
   </si>
@@ -22,46 +22,31 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>Mmp1</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>Bap60</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>cactin</t>
-  </si>
-  <si>
-    <t>PebIII</t>
-  </si>
-  <si>
-    <t>rad50</t>
-  </si>
-  <si>
-    <t>sec23</t>
-  </si>
-  <si>
-    <t>ird5</t>
-  </si>
-  <si>
-    <t>hyd</t>
+    <t>trio</t>
+  </si>
+  <si>
+    <t>Su(z)12</t>
+  </si>
+  <si>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
+  </si>
+  <si>
+    <t>dpld</t>
+  </si>
+  <si>
+    <t>dom</t>
+  </si>
+  <si>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>tld</t>
   </si>
 </sst>
 </file>
@@ -425,39 +410,39 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
